--- a/data/Raw Milk Production - Weekly KPI.xlsx
+++ b/data/Raw Milk Production - Weekly KPI.xlsx
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C1:H162"/>
+  <dimension ref="A1:H162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,12 +610,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Target (gal)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Actual</t>
+          <t>Actual (gal)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -643,7 +643,7 @@
         <v>-4131</v>
       </c>
       <c r="H4" t="n">
-        <v>758.6900000000001</v>
+        <v>6524.73</v>
       </c>
     </row>
     <row r="5">
@@ -660,7 +660,7 @@
         <v>-3978</v>
       </c>
       <c r="H5" t="n">
-        <v>760.22</v>
+        <v>6537.89</v>
       </c>
     </row>
     <row r="6">
@@ -677,7 +677,7 @@
         <v>-4841</v>
       </c>
       <c r="H6" t="n">
-        <v>751.59</v>
+        <v>6463.67</v>
       </c>
     </row>
     <row r="7">
@@ -694,7 +694,7 @@
         <v>-4432</v>
       </c>
       <c r="H7" t="n">
-        <v>755.6799999999999</v>
+        <v>6498.85</v>
       </c>
     </row>
     <row r="8">
@@ -711,7 +711,7 @@
         <v>-3697</v>
       </c>
       <c r="H8" t="n">
-        <v>763.03</v>
+        <v>6562.06</v>
       </c>
     </row>
     <row r="9">
@@ -728,7 +728,7 @@
         <v>-3556</v>
       </c>
       <c r="H9" t="n">
-        <v>764.4400000000001</v>
+        <v>6574.18</v>
       </c>
     </row>
     <row r="10">
@@ -745,7 +745,7 @@
         <v>-4862</v>
       </c>
       <c r="H10" t="n">
-        <v>751.38</v>
+        <v>6461.87</v>
       </c>
     </row>
     <row r="11">
@@ -762,7 +762,7 @@
         <v>-4515</v>
       </c>
       <c r="H11" t="n">
-        <v>754.85</v>
+        <v>6491.71</v>
       </c>
     </row>
     <row r="12">
@@ -779,7 +779,7 @@
         <v>-4643</v>
       </c>
       <c r="H12" t="n">
-        <v>753.5700000000001</v>
+        <v>6480.7</v>
       </c>
     </row>
     <row r="13">
@@ -796,7 +796,7 @@
         <v>-4555</v>
       </c>
       <c r="H13" t="n">
-        <v>754.45</v>
+        <v>6488.27</v>
       </c>
     </row>
     <row r="14">
@@ -813,7 +813,7 @@
         <v>-4887</v>
       </c>
       <c r="H14" t="n">
-        <v>751.13</v>
+        <v>6459.72</v>
       </c>
     </row>
     <row r="15">
@@ -830,7 +830,7 @@
         <v>-5306</v>
       </c>
       <c r="H15" t="n">
-        <v>746.9400000000001</v>
+        <v>6423.68</v>
       </c>
     </row>
     <row r="16">
@@ -847,7 +847,7 @@
         <v>-4744</v>
       </c>
       <c r="H16" t="n">
-        <v>752.5599999999999</v>
+        <v>6472.02</v>
       </c>
     </row>
     <row r="17">
@@ -864,7 +864,7 @@
         <v>-4695</v>
       </c>
       <c r="H17" t="n">
-        <v>753.05</v>
+        <v>6476.23</v>
       </c>
     </row>
     <row r="18">
@@ -881,7 +881,7 @@
         <v>-3641</v>
       </c>
       <c r="H18" t="n">
-        <v>763.59</v>
+        <v>6566.87</v>
       </c>
     </row>
     <row r="19">
@@ -898,7 +898,7 @@
         <v>-3420</v>
       </c>
       <c r="H19" t="n">
-        <v>765.8</v>
+        <v>6585.88</v>
       </c>
     </row>
     <row r="20">
@@ -915,7 +915,7 @@
         <v>-4733</v>
       </c>
       <c r="H20" t="n">
-        <v>752.67</v>
+        <v>6472.96</v>
       </c>
     </row>
     <row r="21">
@@ -932,7 +932,7 @@
         <v>-5501</v>
       </c>
       <c r="H21" t="n">
-        <v>744.99</v>
+        <v>6406.91</v>
       </c>
     </row>
     <row r="22">
@@ -949,7 +949,7 @@
         <v>-4236</v>
       </c>
       <c r="H22" t="n">
-        <v>757.64</v>
+        <v>6515.7</v>
       </c>
     </row>
     <row r="23">
@@ -966,7 +966,7 @@
         <v>-2411</v>
       </c>
       <c r="H23" t="n">
-        <v>775.89</v>
+        <v>6672.65</v>
       </c>
     </row>
     <row r="24">
@@ -983,7 +983,7 @@
         <v>-3196</v>
       </c>
       <c r="H24" t="n">
-        <v>768.04</v>
+        <v>6605.14</v>
       </c>
     </row>
     <row r="25">
@@ -1000,7 +1000,7 @@
         <v>-3283</v>
       </c>
       <c r="H25" t="n">
-        <v>767.17</v>
+        <v>6597.66</v>
       </c>
     </row>
     <row r="26">
@@ -1017,7 +1017,7 @@
         <v>-2669</v>
       </c>
       <c r="H26" t="n">
-        <v>773.3099999999999</v>
+        <v>6650.47</v>
       </c>
     </row>
     <row r="27">
@@ -1034,7 +1034,7 @@
         <v>-2750</v>
       </c>
       <c r="H27" t="n">
-        <v>772.5</v>
+        <v>6643.5</v>
       </c>
     </row>
     <row r="28">
@@ -1051,7 +1051,7 @@
         <v>-4369</v>
       </c>
       <c r="H28" t="n">
-        <v>756.3099999999999</v>
+        <v>6504.27</v>
       </c>
     </row>
     <row r="29">
@@ -1068,7 +1068,7 @@
         <v>-5927</v>
       </c>
       <c r="H29" t="n">
-        <v>740.73</v>
+        <v>6370.28</v>
       </c>
     </row>
     <row r="30">
@@ -1085,7 +1085,7 @@
         <v>-4139</v>
       </c>
       <c r="H30" t="n">
-        <v>758.61</v>
+        <v>6524.05</v>
       </c>
     </row>
     <row r="31">
@@ -1102,7 +1102,7 @@
         <v>-3404</v>
       </c>
       <c r="H31" t="n">
-        <v>765.96</v>
+        <v>6587.26</v>
       </c>
     </row>
     <row r="32">
@@ -1119,7 +1119,7 @@
         <v>-4625</v>
       </c>
       <c r="H32" t="n">
-        <v>753.75</v>
+        <v>6482.25</v>
       </c>
     </row>
     <row r="33">
@@ -1136,7 +1136,7 @@
         <v>-4104</v>
       </c>
       <c r="H33" t="n">
-        <v>758.96</v>
+        <v>6527.06</v>
       </c>
     </row>
     <row r="34">
@@ -1153,7 +1153,7 @@
         <v>-5222</v>
       </c>
       <c r="H34" t="n">
-        <v>747.78</v>
+        <v>6430.91</v>
       </c>
     </row>
     <row r="35">
@@ -1170,7 +1170,7 @@
         <v>-4008</v>
       </c>
       <c r="H35" t="n">
-        <v>759.92</v>
+        <v>6535.31</v>
       </c>
     </row>
     <row r="36">
@@ -1187,7 +1187,7 @@
         <v>-3295</v>
       </c>
       <c r="H36" t="n">
-        <v>767.05</v>
+        <v>6596.63</v>
       </c>
     </row>
     <row r="37">
@@ -1204,7 +1204,7 @@
         <v>-4174</v>
       </c>
       <c r="H37" t="n">
-        <v>758.26</v>
+        <v>6521.04</v>
       </c>
     </row>
     <row r="38">
@@ -1221,7 +1221,7 @@
         <v>-6689</v>
       </c>
       <c r="H38" t="n">
-        <v>733.11</v>
+        <v>6304.75</v>
       </c>
     </row>
     <row r="39">
@@ -1238,7 +1238,7 @@
         <v>-4482</v>
       </c>
       <c r="H39" t="n">
-        <v>755.1799999999999</v>
+        <v>6494.55</v>
       </c>
     </row>
     <row r="40">
@@ -1255,7 +1255,7 @@
         <v>-4218</v>
       </c>
       <c r="H40" t="n">
-        <v>757.8200000000001</v>
+        <v>6517.25</v>
       </c>
     </row>
     <row r="41">
@@ -1272,7 +1272,7 @@
         <v>-4107</v>
       </c>
       <c r="H41" t="n">
-        <v>758.9299999999999</v>
+        <v>6526.8</v>
       </c>
     </row>
     <row r="42">
@@ -1289,7 +1289,7 @@
         <v>-3660</v>
       </c>
       <c r="H42" t="n">
-        <v>763.4</v>
+        <v>6565.24</v>
       </c>
     </row>
     <row r="43">
@@ -1306,7 +1306,7 @@
         <v>-4107</v>
       </c>
       <c r="H43" t="n">
-        <v>758.9299999999999</v>
+        <v>6526.8</v>
       </c>
     </row>
     <row r="44">
@@ -1323,7 +1323,7 @@
         <v>-4099</v>
       </c>
       <c r="H44" t="n">
-        <v>759.01</v>
+        <v>6527.49</v>
       </c>
     </row>
     <row r="45">
@@ -1340,7 +1340,7 @@
         <v>-3811</v>
       </c>
       <c r="H45" t="n">
-        <v>761.89</v>
+        <v>6552.25</v>
       </c>
     </row>
     <row r="46">
@@ -1357,7 +1357,7 @@
         <v>-3638</v>
       </c>
       <c r="H46" t="n">
-        <v>763.62</v>
+        <v>6567.13</v>
       </c>
     </row>
     <row r="47">
@@ -1374,7 +1374,7 @@
         <v>-2935</v>
       </c>
       <c r="H47" t="n">
-        <v>770.65</v>
+        <v>6627.59</v>
       </c>
     </row>
     <row r="48">
@@ -1391,7 +1391,7 @@
         <v>-3150</v>
       </c>
       <c r="H48" t="n">
-        <v>768.5</v>
+        <v>6609.1</v>
       </c>
     </row>
     <row r="49">
@@ -1408,7 +1408,7 @@
         <v>-2606</v>
       </c>
       <c r="H49" t="n">
-        <v>773.9400000000001</v>
+        <v>6655.88</v>
       </c>
     </row>
     <row r="50">
@@ -1425,7 +1425,7 @@
         <v>-4111</v>
       </c>
       <c r="H50" t="n">
-        <v>758.89</v>
+        <v>6526.45</v>
       </c>
     </row>
     <row r="51">
@@ -1442,7 +1442,7 @@
         <v>-5672</v>
       </c>
       <c r="H51" t="n">
-        <v>743.28</v>
+        <v>6392.21</v>
       </c>
     </row>
     <row r="52">
@@ -1459,7 +1459,7 @@
         <v>-4603</v>
       </c>
       <c r="H52" t="n">
-        <v>753.97</v>
+        <v>6484.14</v>
       </c>
     </row>
     <row r="53">
@@ -1476,7 +1476,7 @@
         <v>-5212</v>
       </c>
       <c r="H53" t="n">
-        <v>747.88</v>
+        <v>6431.77</v>
       </c>
     </row>
     <row r="54">
@@ -1493,7 +1493,7 @@
         <v>-4584</v>
       </c>
       <c r="H54" t="n">
-        <v>754.16</v>
+        <v>6485.78</v>
       </c>
     </row>
     <row r="55">
@@ -1510,7 +1510,7 @@
         <v>-4062</v>
       </c>
       <c r="H55" t="n">
-        <v>759.38</v>
+        <v>6530.67</v>
       </c>
     </row>
     <row r="56">
@@ -1527,7 +1527,7 @@
         <v>-2393</v>
       </c>
       <c r="H56" t="n">
-        <v>776.0700000000001</v>
+        <v>6674.2</v>
       </c>
     </row>
     <row r="57">
@@ -1544,7 +1544,7 @@
         <v>-2241</v>
       </c>
       <c r="H57" t="n">
-        <v>777.59</v>
+        <v>6687.27</v>
       </c>
     </row>
     <row r="58">
@@ -1561,7 +1561,7 @@
         <v>-2101</v>
       </c>
       <c r="H58" t="n">
-        <v>778.99</v>
+        <v>6699.31</v>
       </c>
     </row>
     <row r="59">
@@ -1578,7 +1578,7 @@
         <v>-3624</v>
       </c>
       <c r="H59" t="n">
-        <v>763.76</v>
+        <v>6568.34</v>
       </c>
     </row>
     <row r="60">
@@ -1595,7 +1595,7 @@
         <v>-2551</v>
       </c>
       <c r="H60" t="n">
-        <v>774.49</v>
+        <v>6660.61</v>
       </c>
     </row>
     <row r="61">
@@ -1612,7 +1612,7 @@
         <v>-1521</v>
       </c>
       <c r="H61" t="n">
-        <v>784.79</v>
+        <v>6749.19</v>
       </c>
     </row>
     <row r="62">
@@ -1629,7 +1629,7 @@
         <v>-987</v>
       </c>
       <c r="H62" t="n">
-        <v>790.13</v>
+        <v>6795.12</v>
       </c>
     </row>
     <row r="63">
@@ -1646,7 +1646,7 @@
         <v>-730</v>
       </c>
       <c r="H63" t="n">
-        <v>792.7</v>
+        <v>6817.22</v>
       </c>
     </row>
     <row r="64">
@@ -1663,7 +1663,7 @@
         <v>-261</v>
       </c>
       <c r="H64" t="n">
-        <v>797.39</v>
+        <v>6857.55</v>
       </c>
     </row>
     <row r="65">
@@ -1680,7 +1680,7 @@
         <v>-116</v>
       </c>
       <c r="H65" t="n">
-        <v>798.84</v>
+        <v>6870.02</v>
       </c>
     </row>
     <row r="66">
@@ -1697,7 +1697,7 @@
         <v>463</v>
       </c>
       <c r="H66" t="n">
-        <v>804.63</v>
+        <v>6919.82</v>
       </c>
     </row>
     <row r="67">
@@ -1714,7 +1714,7 @@
         <v>-309</v>
       </c>
       <c r="H67" t="n">
-        <v>796.91</v>
+        <v>6853.43</v>
       </c>
     </row>
     <row r="68">
@@ -1731,7 +1731,7 @@
         <v>-1018</v>
       </c>
       <c r="H68" t="n">
-        <v>789.8200000000001</v>
+        <v>6792.45</v>
       </c>
     </row>
     <row r="69">
@@ -1748,7 +1748,7 @@
         <v>-2812</v>
       </c>
       <c r="H69" t="n">
-        <v>771.88</v>
+        <v>6638.17</v>
       </c>
     </row>
     <row r="70">
@@ -1765,7 +1765,7 @@
         <v>-3198</v>
       </c>
       <c r="H70" t="n">
-        <v>768.02</v>
+        <v>6604.97</v>
       </c>
     </row>
     <row r="71">
@@ -1782,7 +1782,7 @@
         <v>-3442</v>
       </c>
       <c r="H71" t="n">
-        <v>765.58</v>
+        <v>6583.99</v>
       </c>
     </row>
     <row r="72">
@@ -1799,7 +1799,7 @@
         <v>-2785</v>
       </c>
       <c r="H72" t="n">
-        <v>772.15</v>
+        <v>6640.49</v>
       </c>
     </row>
     <row r="73">
@@ -1816,7 +1816,7 @@
         <v>-2585</v>
       </c>
       <c r="H73" t="n">
-        <v>774.15</v>
+        <v>6657.69</v>
       </c>
     </row>
     <row r="74">
@@ -1833,7 +1833,7 @@
         <v>-2810.918604651175</v>
       </c>
       <c r="H74" t="n">
-        <v>771.89</v>
+        <v>6638.26</v>
       </c>
     </row>
     <row r="75">
@@ -1850,7 +1850,7 @@
         <v>-1957.895348837206</v>
       </c>
       <c r="H75" t="n">
-        <v>780.42</v>
+        <v>6711.62</v>
       </c>
     </row>
     <row r="76">
@@ -1867,7 +1867,7 @@
         <v>-1918.325581395344</v>
       </c>
       <c r="H76" t="n">
-        <v>780.8200000000001</v>
+        <v>6715.02</v>
       </c>
     </row>
     <row r="77">
@@ -1884,7 +1884,7 @@
         <v>-748.8023255814041</v>
       </c>
       <c r="H77" t="n">
-        <v>792.51</v>
+        <v>6815.6</v>
       </c>
     </row>
     <row r="78">
@@ -1901,7 +1901,7 @@
         <v>-2055.813953488367</v>
       </c>
       <c r="H78" t="n">
-        <v>779.4400000000001</v>
+        <v>6703.2</v>
       </c>
     </row>
     <row r="79">
@@ -1918,7 +1918,7 @@
         <v>183.4883720930229</v>
       </c>
       <c r="H79" t="n">
-        <v>801.83</v>
+        <v>6895.78</v>
       </c>
     </row>
     <row r="80">
@@ -1935,7 +1935,7 @@
         <v>-288.9534883720917</v>
       </c>
       <c r="H80" t="n">
-        <v>797.11</v>
+        <v>6855.15</v>
       </c>
     </row>
     <row r="81">
@@ -1952,7 +1952,7 @@
         <v>-3464.767441860473</v>
       </c>
       <c r="H81" t="n">
-        <v>765.35</v>
+        <v>6582.03</v>
       </c>
     </row>
     <row r="82">
@@ -1969,7 +1969,7 @@
         <v>-1521.627906976733</v>
       </c>
       <c r="H82" t="n">
-        <v>784.78</v>
+        <v>6749.14</v>
       </c>
     </row>
     <row r="83">
@@ -1986,7 +1986,7 @@
         <v>-467.3953488372063</v>
       </c>
       <c r="H83" t="n">
-        <v>795.33</v>
+        <v>6839.8</v>
       </c>
     </row>
     <row r="84">
@@ -2003,7 +2003,7 @@
         <v>-1364.872093023252</v>
       </c>
       <c r="H84" t="n">
-        <v>786.35</v>
+        <v>6762.62</v>
       </c>
     </row>
     <row r="85">
@@ -2020,7 +2020,7 @@
         <v>-769.6744186046417</v>
       </c>
       <c r="H85" t="n">
-        <v>792.3</v>
+        <v>6813.81</v>
       </c>
     </row>
     <row r="86">
@@ -2037,7 +2037,7 @@
         <v>-2707.069767441862</v>
       </c>
       <c r="H86" t="n">
-        <v>772.9299999999999</v>
+        <v>6647.19</v>
       </c>
     </row>
     <row r="87">
@@ -2054,7 +2054,7 @@
         <v>-248.139534883725</v>
       </c>
       <c r="H87" t="n">
-        <v>797.52</v>
+        <v>6858.66</v>
       </c>
     </row>
     <row r="88">
@@ -2071,7 +2071,7 @@
         <v>-2315.069767441862</v>
       </c>
       <c r="H88" t="n">
-        <v>776.85</v>
+        <v>6680.9</v>
       </c>
     </row>
     <row r="89">
@@ -2088,7 +2088,7 @@
         <v>-692.27906976745</v>
       </c>
       <c r="H89" t="n">
-        <v>793.08</v>
+        <v>6820.46</v>
       </c>
     </row>
     <row r="90">
@@ -2105,7 +2105,7 @@
         <v>104.6046511627937</v>
       </c>
       <c r="H90" t="n">
-        <v>801.05</v>
+        <v>6889</v>
       </c>
     </row>
     <row r="91">
@@ -2122,7 +2122,7 @@
         <v>541.5116279069916</v>
       </c>
       <c r="H91" t="n">
-        <v>805.42</v>
+        <v>6926.57</v>
       </c>
     </row>
     <row r="92">
@@ -2139,7 +2139,7 @@
         <v>1390.860465116275</v>
       </c>
       <c r="H92" t="n">
-        <v>813.91</v>
+        <v>6999.61</v>
       </c>
     </row>
     <row r="93">
@@ -2156,7 +2156,7 @@
         <v>592.3837209302292</v>
       </c>
       <c r="H93" t="n">
-        <v>805.92</v>
+        <v>6930.94</v>
       </c>
     </row>
     <row r="94">
@@ -2173,7 +2173,7 @@
         <v>73.55813953489996</v>
       </c>
       <c r="H94" t="n">
-        <v>800.74</v>
+        <v>6886.33</v>
       </c>
     </row>
     <row r="95">
@@ -2190,7 +2190,7 @@
         <v>264.4534883721062</v>
       </c>
       <c r="H95" t="n">
-        <v>802.64</v>
+        <v>6902.74</v>
       </c>
     </row>
     <row r="96">
@@ -2207,7 +2207,7 @@
         <v>-490.2674418604729</v>
       </c>
       <c r="H96" t="n">
-        <v>795.1</v>
+        <v>6837.84</v>
       </c>
     </row>
     <row r="97">
@@ -2224,7 +2224,7 @@
         <v>-527.3372093023208</v>
       </c>
       <c r="H97" t="n">
-        <v>794.73</v>
+        <v>6834.65</v>
       </c>
     </row>
     <row r="98">
@@ -2241,7 +2241,7 @@
         <v>-787.9186046511604</v>
       </c>
       <c r="H98" t="n">
-        <v>792.12</v>
+        <v>6812.24</v>
       </c>
     </row>
     <row r="99">
@@ -2258,7 +2258,7 @@
         <v>-472.3488372092979</v>
       </c>
       <c r="H99" t="n">
-        <v>795.28</v>
+        <v>6839.38</v>
       </c>
     </row>
     <row r="100">
@@ -2275,7 +2275,7 @@
         <v>-786.0581395348854</v>
       </c>
       <c r="H100" t="n">
-        <v>792.14</v>
+        <v>6812.4</v>
       </c>
     </row>
     <row r="101">
@@ -2292,7 +2292,7 @@
         <v>-570.360465116275</v>
       </c>
       <c r="H101" t="n">
-        <v>794.3</v>
+        <v>6830.95</v>
       </c>
     </row>
     <row r="102">
@@ -2309,7 +2309,7 @@
         <v>-1492.406976744169</v>
       </c>
       <c r="H102" t="n">
-        <v>785.08</v>
+        <v>6751.65</v>
       </c>
     </row>
     <row r="103">
@@ -2326,7 +2326,7 @@
         <v>-1796.790697674413</v>
       </c>
       <c r="H103" t="n">
-        <v>782.03</v>
+        <v>6725.48</v>
       </c>
     </row>
     <row r="104">
@@ -2343,7 +2343,7 @@
         <v>-1635.406976744183</v>
       </c>
       <c r="H104" t="n">
-        <v>783.65</v>
+        <v>6739.35</v>
       </c>
     </row>
     <row r="105">
@@ -2360,7 +2360,7 @@
         <v>-1121.186046511619</v>
       </c>
       <c r="H105" t="n">
-        <v>788.79</v>
+        <v>6783.58</v>
       </c>
     </row>
     <row r="106">
@@ -2377,7 +2377,7 @@
         <v>-467.3372093023208</v>
       </c>
       <c r="H106" t="n">
-        <v>795.33</v>
+        <v>6839.81</v>
       </c>
     </row>
     <row r="107">
@@ -2394,7 +2394,7 @@
         <v>739.0232558139542</v>
       </c>
       <c r="H107" t="n">
-        <v>807.39</v>
+        <v>6943.56</v>
       </c>
     </row>
     <row r="108">
@@ -2411,7 +2411,7 @@
         <v>368.6046511627937</v>
       </c>
       <c r="H108" t="n">
-        <v>803.6900000000001</v>
+        <v>6911.7</v>
       </c>
     </row>
     <row r="109">
@@ -2428,7 +2428,7 @@
         <v>-1496.30232558139</v>
       </c>
       <c r="H109" t="n">
-        <v>810.04</v>
+        <v>6966.32</v>
       </c>
     </row>
     <row r="110">
@@ -2445,7 +2445,7 @@
         <v>-1957.418604651146</v>
       </c>
       <c r="H110" t="n">
-        <v>805.4299999999999</v>
+        <v>6926.66</v>
       </c>
     </row>
     <row r="111">
@@ -2462,7 +2462,7 @@
         <v>-4290.965116279083</v>
       </c>
       <c r="H111" t="n">
-        <v>782.09</v>
+        <v>6725.98</v>
       </c>
     </row>
     <row r="112">
@@ -2479,7 +2479,7 @@
         <v>-3051.034883720931</v>
       </c>
       <c r="H112" t="n">
-        <v>794.49</v>
+        <v>6832.61</v>
       </c>
     </row>
     <row r="113">
@@ -2496,7 +2496,7 @@
         <v>-2869</v>
       </c>
       <c r="H113" t="n">
-        <v>796.3099999999999</v>
+        <v>6848.27</v>
       </c>
     </row>
     <row r="114">
@@ -2513,7 +2513,7 @@
         <v>-3639</v>
       </c>
       <c r="H114" t="n">
-        <v>788.61</v>
+        <v>6782.05</v>
       </c>
     </row>
     <row r="115">
@@ -2530,7 +2530,7 @@
         <v>-3350</v>
       </c>
       <c r="H115" t="n">
-        <v>791.5</v>
+        <v>6806.9</v>
       </c>
     </row>
     <row r="116">
@@ -2547,7 +2547,7 @@
         <v>-2282</v>
       </c>
       <c r="H116" t="n">
-        <v>802.1799999999999</v>
+        <v>6898.75</v>
       </c>
     </row>
     <row r="117">
@@ -2564,7 +2564,7 @@
         <v>-2292.790697674413</v>
       </c>
       <c r="H117" t="n">
-        <v>802.0700000000001</v>
+        <v>6897.82</v>
       </c>
     </row>
     <row r="118">
@@ -2581,7 +2581,7 @@
         <v>-2976.046511627908</v>
       </c>
       <c r="H118" t="n">
-        <v>795.24</v>
+        <v>6839.06</v>
       </c>
     </row>
     <row r="119">
@@ -2598,7 +2598,7 @@
         <v>-2116.627906976748</v>
       </c>
       <c r="H119" t="n">
-        <v>803.83</v>
+        <v>6912.97</v>
       </c>
     </row>
     <row r="120">
@@ -2615,7 +2615,7 @@
         <v>-1252.209302325573</v>
       </c>
       <c r="H120" t="n">
-        <v>812.48</v>
+        <v>6987.31</v>
       </c>
     </row>
     <row r="121">
@@ -2632,7 +2632,7 @@
         <v>-51.51162790697708</v>
       </c>
       <c r="H121" t="n">
-        <v>824.48</v>
+        <v>7090.57</v>
       </c>
     </row>
     <row r="122">
@@ -2649,7 +2649,7 @@
         <v>-701.1627906976646</v>
       </c>
       <c r="H122" t="n">
-        <v>817.99</v>
+        <v>7034.7</v>
       </c>
     </row>
     <row r="123">
@@ -2666,7 +2666,7 @@
         <v>-349.1860465116188</v>
       </c>
       <c r="H123" t="n">
-        <v>821.51</v>
+        <v>7064.97</v>
       </c>
     </row>
     <row r="124">
@@ -2683,7 +2683,7 @@
         <v>-789.3023255813896</v>
       </c>
       <c r="H124" t="n">
-        <v>817.11</v>
+        <v>7027.12</v>
       </c>
     </row>
     <row r="125">
@@ -2700,7 +2700,7 @@
         <v>636.9767441860458</v>
       </c>
       <c r="H125" t="n">
-        <v>831.37</v>
+        <v>7149.78</v>
       </c>
     </row>
     <row r="126">
@@ -2717,7 +2717,7 @@
         <v>21</v>
       </c>
       <c r="H126" t="n">
-        <v>825.21</v>
+        <v>7096.81</v>
       </c>
     </row>
     <row r="127">
@@ -2734,7 +2734,7 @@
         <v>-1032</v>
       </c>
       <c r="H127" t="n">
-        <v>814.6799999999999</v>
+        <v>7006.25</v>
       </c>
     </row>
     <row r="128">
@@ -2751,7 +2751,7 @@
         <v>137</v>
       </c>
       <c r="H128" t="n">
-        <v>826.37</v>
+        <v>7106.78</v>
       </c>
     </row>
     <row r="129">
@@ -2768,7 +2768,7 @@
         <v>585</v>
       </c>
       <c r="H129" t="n">
-        <v>830.85</v>
+        <v>7145.31</v>
       </c>
     </row>
     <row r="130">
@@ -2785,7 +2785,7 @@
         <v>1767</v>
       </c>
       <c r="H130" t="n">
-        <v>842.67</v>
+        <v>7246.96</v>
       </c>
     </row>
     <row r="131">
@@ -2802,7 +2802,7 @@
         <v>1287</v>
       </c>
       <c r="H131" t="n">
-        <v>837.87</v>
+        <v>7205.68</v>
       </c>
     </row>
     <row r="132">
@@ -2819,7 +2819,7 @@
         <v>1036</v>
       </c>
       <c r="H132" t="n">
-        <v>835.36</v>
+        <v>7184.1</v>
       </c>
     </row>
     <row r="133">
@@ -2836,7 +2836,7 @@
         <v>309</v>
       </c>
       <c r="H133" t="n">
-        <v>828.09</v>
+        <v>7121.57</v>
       </c>
     </row>
     <row r="134">
@@ -2853,7 +2853,7 @@
         <v>-169</v>
       </c>
       <c r="H134" t="n">
-        <v>823.3099999999999</v>
+        <v>7080.47</v>
       </c>
     </row>
     <row r="135">
@@ -2870,7 +2870,7 @@
         <v>-799</v>
       </c>
       <c r="H135" t="n">
-        <v>817.01</v>
+        <v>7026.29</v>
       </c>
     </row>
     <row r="136">
@@ -2887,7 +2887,7 @@
         <v>1063</v>
       </c>
       <c r="H136" t="n">
-        <v>835.63</v>
+        <v>7186.42</v>
       </c>
     </row>
     <row r="137">
@@ -2904,7 +2904,7 @@
         <v>692</v>
       </c>
       <c r="H137" t="n">
-        <v>831.92</v>
+        <v>7154.51</v>
       </c>
     </row>
     <row r="138">
@@ -2921,7 +2921,7 @@
         <v>2802</v>
       </c>
       <c r="H138" t="n">
-        <v>853.02</v>
+        <v>7335.97</v>
       </c>
     </row>
     <row r="139">
